--- a/data/trans_dic/IP13-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,99</t>
+          <t>2,06; 6,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,24</t>
+          <t>2,49; 8,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,65</t>
+          <t>1,35; 6,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,19</t>
+          <t>2,26; 9,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,28</t>
+          <t>2,92; 9,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,99</t>
+          <t>3,11; 10,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,84</t>
+          <t>1,04; 5,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,26</t>
+          <t>2,06; 8,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,14</t>
+          <t>3,08; 7,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,26</t>
+          <t>3,47; 8,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,41</t>
+          <t>1,68; 5,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,16</t>
+          <t>2,85; 7,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,43</t>
+          <t>3,75; 8,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,38</t>
+          <t>3,15; 8,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,9</t>
+          <t>2,99; 8,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,79</t>
+          <t>3,52; 8,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,59</t>
+          <t>3,14; 8,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,46</t>
+          <t>4,14; 9,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,94</t>
+          <t>3,79; 8,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,33</t>
+          <t>3,2; 8,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,63</t>
+          <t>3,78; 7,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,8</t>
+          <t>4,15; 7,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,51</t>
+          <t>3,82; 7,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,26</t>
+          <t>3,82; 7,76</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,46</t>
+          <t>2,86; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,59</t>
+          <t>6,15; 13,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,3</t>
+          <t>3,49; 9,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,81</t>
+          <t>4,51; 12,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,78</t>
+          <t>3,95; 10,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 13,43</t>
+          <t>2,51; 8,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,0</t>
+          <t>3,83; 9,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 12,02</t>
+          <t>4,66; 12,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,43</t>
+          <t>3,95; 8,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,52</t>
+          <t>5,11; 9,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,44</t>
+          <t>4,33; 8,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,83</t>
+          <t>5,4; 10,54</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,93</t>
+          <t>2,63; 7,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,21</t>
+          <t>3,23; 8,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,75</t>
+          <t>1,47; 5,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,08</t>
+          <t>5,28; 12,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,33</t>
+          <t>0,7; 3,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,36</t>
+          <t>2,42; 7,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,83</t>
+          <t>3,22; 8,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,27</t>
+          <t>3,31; 9,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,78</t>
+          <t>2,0; 4,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,21</t>
+          <t>3,35; 7,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,06</t>
+          <t>2,7; 6,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,77</t>
+          <t>4,99; 9,63</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,77</t>
+          <t>3,79; 6,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,12</t>
+          <t>4,81; 7,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,7</t>
+          <t>3,27; 5,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,1</t>
+          <t>5,11; 8,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,3</t>
+          <t>3,22; 5,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,77</t>
+          <t>4,19; 7,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,79</t>
+          <t>4,03; 6,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,08</t>
+          <t>4,46; 7,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,71</t>
+          <t>3,84; 5,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,96</t>
+          <t>4,8; 6,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,77</t>
+          <t>4,04; 5,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,18</t>
+          <t>5,13; 7,51</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7347</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4774</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7619</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8756</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4046</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5263</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11370</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4133; 13855</t>
+          <t>3153; 10665</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4626; 15659</t>
+          <t>3824; 13097</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1485; 8891</t>
+          <t>2003; 10266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2279; 9601</t>
+          <t>2828; 11856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2976; 11149</t>
+          <t>4045; 13137</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3778; 12281</t>
+          <t>4331; 15267</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1936; 10134</t>
+          <t>1395; 7920</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2690; 11536</t>
+          <t>2495; 10690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8569; 20839</t>
+          <t>8987; 20793</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9785; 24205</t>
+          <t>10160; 24145</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4546; 15256</t>
+          <t>4723; 15008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6679; 18407</t>
+          <t>7012; 18020</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12638</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11858</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13198</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9958</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13041</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12175</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10520</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12638</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11858</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11602</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>22808</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6126; 16461</t>
+          <t>7946; 18756</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8410; 19248</t>
+          <t>7048; 19014</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7944; 18440</t>
+          <t>6710; 18135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6269; 16745</t>
+          <t>8356; 20277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7448; 18221</t>
+          <t>6134; 15628</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7052; 18946</t>
+          <t>8500; 19964</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7334; 17822</t>
+          <t>7853; 18344</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8225; 21236</t>
+          <t>5893; 15426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16208; 31062</t>
+          <t>15385; 30279</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17082; 33461</t>
+          <t>17806; 33187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17423; 32420</t>
+          <t>16474; 31478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17292; 32349</t>
+          <t>16119; 32700</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7931</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15268</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10247</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12745</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>9087</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7456</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9779</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7931</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15268</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10247</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>24823</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5492; 14410</t>
+          <t>4287; 12806</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3562; 13340</t>
+          <t>10156; 22483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6095; 16069</t>
+          <t>5811; 16187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5785; 18592</t>
+          <t>7599; 20779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4456; 13139</t>
+          <t>5440; 14741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10731; 22189</t>
+          <t>3893; 12548</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6211; 16665</t>
+          <t>5971; 15236</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8699; 22264</t>
+          <t>7275; 20205</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11351; 24231</t>
+          <t>11344; 25189</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15633; 30518</t>
+          <t>16387; 31223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13952; 27225</t>
+          <t>13958; 27991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17952; 36859</t>
+          <t>17533; 34214</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9514</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13811</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3747</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9368</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11064</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10011</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9514</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11627</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>23408</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1426; 8229</t>
+          <t>5456; 15520</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5288; 15160</t>
+          <t>6708; 18224</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6457; 18156</t>
+          <t>3034; 11690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6237; 16937</t>
+          <t>8942; 20783</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4848; 15233</t>
+          <t>1464; 8343</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6996; 19445</t>
+          <t>5093; 15534</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3154; 12000</t>
+          <t>6681; 17212</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9229; 22232</t>
+          <t>5527; 15682</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8889; 19918</t>
+          <t>8334; 20089</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14497; 30154</t>
+          <t>14015; 29546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11294; 25017</t>
+          <t>11137; 25433</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17428; 34131</t>
+          <t>16793; 32410</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22650; 39327</t>
+          <t>27358; 46481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29857; 50555</t>
+          <t>36103; 57724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28561; 47171</t>
+          <t>24341; 43080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28000; 47236</t>
+          <t>35761; 58317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27185; 45549</t>
+          <t>21917; 39561</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36046; 58334</t>
+          <t>29760; 50695</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24044; 43119</t>
+          <t>28392; 46841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37418; 61482</t>
+          <t>28041; 47758</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54060; 80167</t>
+          <t>53897; 78900</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71740; 101689</t>
+          <t>70068; 100074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57615; 83620</t>
+          <t>58617; 86489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71550; 102444</t>
+          <t>68193; 99884</t>
         </is>
       </c>
     </row>
